--- a/bd_fournisseurs.xlsx
+++ b/bd_fournisseurs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,30 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Compte TVA</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Nom de la banque</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>NPA/Ville banque</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>No de compte</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>IBAN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
@@ -528,65 +533,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beta Ltd</t>
+          <t>A Supplier 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Responsable 2</t>
+          <t>Contact A1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2 Rue Fictive</t>
+          <t>1 A Street</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1002 Ville2</t>
+          <t>1000-ACity</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+41 22 345 67 02</t>
+          <t>012345600</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+41 22 765 43 02</t>
+          <t>065432100</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>www.fournisseur2.com</t>
+          <t>www.asupplier1.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>contact@fournisseur2.com</t>
+          <t>contacta1@example.com</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CCREDIT2</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CDEBIT2</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>30</t>
@@ -594,185 +603,163 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2002 VilleB2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 902</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 002 1234 5</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Charlie Solutions</t>
+          <t>A Supplier 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Responsable 3</t>
+          <t>Contact A2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3 Rue Fictive</t>
+          <t>1 A Avenue</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1003 Ville3</t>
+          <t>2000-AVille</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+41 22 345 67 03</t>
+          <t>023456700</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+41 22 765 43 03</t>
+          <t>076543200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>www.fournisseur3.com</t>
+          <t>www.asupplier2.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>contact@fournisseur3.com</t>
+          <t>contacta2@example.com</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CCREDIT3</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CDEBIT3</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2003 VilleB3</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 903</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 003 1234 5</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Delta Enterprises</t>
+          <t>B Supplier 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Responsable 4</t>
+          <t>Contact B1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4 Rue Fictive</t>
+          <t>2 B Street</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1004 Ville4</t>
+          <t>1001-BCity</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+41 22 345 67 04</t>
+          <t>012345601</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+41 22 765 43 04</t>
+          <t>065432101</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>www.fournisseur4.com</t>
+          <t>www.bsupplier1.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>contact@fournisseur4.com</t>
+          <t>contactb1@example.com</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CCREDIT4</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CDEBIT4</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>30</t>
@@ -780,185 +767,163 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2004 VilleB4</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 904</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 004 1234 5</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Echo Industries</t>
+          <t>B Supplier 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Responsable 5</t>
+          <t>Contact B2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5 Rue Fictive</t>
+          <t>2 B Avenue</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1005 Ville5</t>
+          <t>2001-BVille</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+41 22 345 67 05</t>
+          <t>023456701</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+41 22 765 43 05</t>
+          <t>076543201</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>www.fournisseur5.com</t>
+          <t>www.bsupplier2.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>contact@fournisseur5.com</t>
+          <t>contactb2@example.com</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000 - Caisse - </t>
+          <t>2101</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1500 - Intitulé du compte - 15</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3.6 (%)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2005 VilleB5</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 905</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 005 1234 5</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>je m'aime quand tout marche!</t>
-        </is>
-      </c>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>0003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foxtrot Systems</t>
+          <t>C Supplier 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Responsable 6</t>
+          <t>Contact C1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6 Rue Fictive</t>
+          <t>3 C Street</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1006 Ville6</t>
+          <t>1002-CCity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+41 22 345 67 06</t>
+          <t>012345602</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+41 22 765 43 06</t>
+          <t>065432102</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>www.fournisseur6.com</t>
+          <t>www.csupplier1.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>contact@fournisseur6.com</t>
+          <t>contactc1@example.com</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CCREDIT6</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CDEBIT6</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>30</t>
@@ -966,185 +931,163 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2006 VilleB6</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 906</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 006 1234 5</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gamma Tech</t>
+          <t>C Supplier 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Responsable 7</t>
+          <t>Contact C2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7 Rue Fictive</t>
+          <t>3 C Avenue</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1007 Ville7</t>
+          <t>2002-CVille</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+41 22 345 67 07</t>
+          <t>023456702</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+41 22 765 43 07</t>
+          <t>076543202</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>www.fournisseur7.com</t>
+          <t>www.csupplier2.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>contact@fournisseur7.com</t>
+          <t>contactc2@example.com</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CCREDIT7</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CDEBIT7</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2007 VilleB7</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 907</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 007 1234 5</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hotel Consulting</t>
+          <t>D Supplier 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Responsable 8</t>
+          <t>Contact D1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8 Rue Fictive</t>
+          <t>4 D Street</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1008 Ville8</t>
+          <t>1003-DCity</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+41 22 345 67 08</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+41 22 765 43 08</t>
+          <t>065432103</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>www.fournisseur8.com</t>
+          <t>www.dsupplier1.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>contact@fournisseur8.com</t>
+          <t>contactd1@example.com</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CCREDIT8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>CDEBIT8</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>30</t>
@@ -1152,185 +1095,163 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2008 VilleB8</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 908</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 008 1234 5</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>India Group</t>
+          <t>D Supplier 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Responsable 9</t>
+          <t>Contact D2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9 Rue Fictive</t>
+          <t>4 D Avenue</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1009 Ville9</t>
+          <t>2003-DVille</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+41 22 345 67 09</t>
+          <t>023456703</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+41 22 765 43 09</t>
+          <t>076543203</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>www.fournisseur9.com</t>
+          <t>www.dsupplier2.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>contact@fournisseur9.com</t>
+          <t>contactd2@example.com</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CCREDIT9</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CDEBIT9</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2009 VilleB9</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 909</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 009 1234 5</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>0005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Juliet Services</t>
+          <t>E Supplier 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Responsable 10</t>
+          <t>Contact E1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10 Rue Fictive</t>
+          <t>5 E Street</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10010 Ville10 +10</t>
+          <t>1004-ECity</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+41 22 345 67 10</t>
+          <t>012345604</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+41 22 765 43 10</t>
+          <t>065432104</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>www.fournisseur10.com</t>
+          <t>www.esupplier1.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>contact@fournisseur10.com</t>
+          <t>contacte1@example.com</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002 - Créances clients - </t>
+          <t>2004</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1402 - Intitulé du compte - 14</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0 (%)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>30</t>
@@ -1338,185 +1259,163 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>20010 VilleB10</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9010</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0010 1234 5</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>E005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kilo Works</t>
+          <t>E Supplier 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Responsable 11</t>
+          <t>Contact E2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11 Rue Fictive</t>
+          <t>5 E Avenue</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10011 Ville11</t>
+          <t>2004-EVille</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+41 22 345 67 11</t>
+          <t>023456704</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+41 22 765 43 11</t>
+          <t>076543204</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>www.fournisseur11.com</t>
+          <t>www.esupplier2.com</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>contact@fournisseur11.com</t>
+          <t>contacte2@example.com</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CCREDIT11</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CDEBIT11</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>20011 VilleB11</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9011</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0011 1234 5</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>0006</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lima Digital</t>
+          <t>F Supplier 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Responsable 12</t>
+          <t>Contact F1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12 Rue Fictive</t>
+          <t>6 F Street</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10012 Ville12</t>
+          <t>1005-FCity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+41 22 345 67 12</t>
+          <t>012345605</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+41 22 765 43 12</t>
+          <t>065432105</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>www.fournisseur12.com</t>
+          <t>www.fsupplier1.com</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>contact@fournisseur12.com</t>
+          <t>contactf1@example.com</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CCREDIT12</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CDEBIT12</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>30</t>
@@ -1524,185 +1423,163 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>20012 VilleB12</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9012</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0012 1234 5</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F006</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mike Networks</t>
+          <t>F Supplier 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Responsable 13</t>
+          <t>Contact F2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13 Rue Fictive</t>
+          <t>6 F Avenue</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10013 Ville13</t>
+          <t>2005-FVille</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+41 22 345 67 13</t>
+          <t>023456705</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+41 22 765 43 13</t>
+          <t>076543205</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>www.fournisseur13.com</t>
+          <t>www.fsupplier2.com</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>contact@fournisseur13.com</t>
+          <t>contactf2@example.com</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CCREDIT13</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CDEBIT13</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>20013 VilleB13</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9013</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0013 1234 5</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>November Goods</t>
+          <t>G Supplier 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Responsable 14</t>
+          <t>Contact G1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14 Rue Fictive</t>
+          <t>7 G Street</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10014 Ville14</t>
+          <t>1006-GCity</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+41 22 345 67 14</t>
+          <t>012345606</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+41 22 765 43 14</t>
+          <t>065432106</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>www.fournisseur14.com</t>
+          <t>www.gsupplier1.com</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>contact@fournisseur14.com</t>
+          <t>contactg1@example.com</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001 - Banque - </t>
+          <t>2006</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1502 - Intitulé du compte - 15</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5.2 (%)</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>30</t>
@@ -1710,303 +1587,327 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>20014 VilleB14</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9014</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0014 1234 5</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oscar Supplies</t>
+          <t>G Supplier 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Responsable 15</t>
+          <t>Contact G2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15 Rue Fictive</t>
+          <t>7 G Avenue</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10015 Ville15</t>
+          <t>2006-GVille</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+41 22 345 67 15</t>
+          <t>023456706</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+41 22 765 43 15</t>
+          <t>076543206</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>www.fournisseur15.com</t>
+          <t>www.gsupplier2.com</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>contact@fournisseur15.com</t>
+          <t>contactg2@example.com</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CCREDIT15</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CDEBIT15</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>20015 VilleB15</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9015</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0015 1234 5</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F016</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H Supplier 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Contact H1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 H Street</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1007-HCity</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>012345607</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>065432107</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>www.hsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>contacth1@example.com</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4007</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>H008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quebec Trade</t>
+          <t>H Supplier 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Responsable 17</t>
+          <t>Contact H2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17 Rue Fictive</t>
+          <t>8 H Avenue</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10017 Ville17</t>
+          <t>2007-HVille</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+41 22 345 67 17</t>
+          <t>023456707</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+41 22 765 43 17</t>
+          <t>076543207</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>www.fournisseur17.com</t>
+          <t>www.hsupplier2.com</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>contact@fournisseur17.com</t>
+          <t>contacth2@example.com</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CCREDIT17</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CDEBIT17</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>20017 VilleB17</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9017</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0017 1234 5</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4107</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>0009</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Romeo Ventures</t>
+          <t>I Supplier 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Responsable 18</t>
+          <t>Contact I1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18 Rue Fictive</t>
+          <t>9 I Street</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10018 Ville18</t>
+          <t>1008-ICity</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+41 22 345 67 18</t>
+          <t>012345608</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+41 22 765 43 18</t>
+          <t>065432108</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>www.fournisseur18.com</t>
+          <t>www.isupplier1.com</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>contact@fournisseur18.com</t>
+          <t>contacti1@example.com</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CCREDIT18</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>CDEBIT18</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>30</t>
@@ -2014,757 +1915,981 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>20018 VilleB18</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9018</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0018 1234 5</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>I009</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sierra Technologies</t>
+          <t>I Supplier 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Responsable 19</t>
+          <t>Contact I2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19 Rue Fictive</t>
+          <t>9 I Avenue</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10019 Ville19</t>
+          <t>2008-IVille</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+41 22 345 67 19</t>
+          <t>023456708</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+41 22 765 43 19</t>
+          <t>076543208</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>www.fournisseur19.com</t>
+          <t>www.isupplier2.com</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>contact@fournisseur19.com</t>
+          <t>contacti2@example.com</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CCREDIT19</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CDEBIT19</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Banque Fictive</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>20019 VilleB19</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CH00 1234 5678 9019</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>CH93 0000 0000 0019 1234 5</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">bla bla   ba ba ba </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>J Supplier 1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Contact J1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10 J Street</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1001 toto</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>1009-JCity</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>012345609</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>065432109</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>www.jsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>contactj1@example.com</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CCREDIT30</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CDEBIT1234567</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dacia</t>
+          <t>J010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>J Supplier 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>Contact J2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>10 J Avenue</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>saadia</t>
+          <t>2009-JVille</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>023456709</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>076543209</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>www.jsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>contactj2@example.com</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004 - Stocks - </t>
+          <t>2109</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1010 - Intitulé du compte - 10</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4109</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>éh</t>
+          <t>0011</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>uzg</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>K Supplier 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Contact K1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>11 K Street</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>gé</t>
+          <t>1010-KCity</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>igé</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>012345610</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>065432110</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>www.ksupplier1.com</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>contactk1@example.com</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1010 - Intitulé du compte - 10</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>4010</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>éh</t>
+          <t>K011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>uzg</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>K Supplier 2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Contact K2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>11 K Avenue</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>gé</t>
+          <t>2010-KVille</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>igé</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>023456710</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>076543210</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>www.ksupplier2.com</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>contactk2@example.com</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1010 - Intitulé du compte - 10</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>weafrwer</t>
+          <t>0012</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>afsadasdf</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>L Supplier 1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Contact L1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>12 L Street</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>afa</t>
+          <t>1011-LCity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>asdf</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>012345611</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>065432111</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>www.lsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>contactl1@example.com</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>4011</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>L012</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>L Supplier 2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Contact L2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>12 L Avenue</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>2011-LVille</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>023456711</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>076543211</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>www.lsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>contactl2@example.com</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>M Supplier 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Contact M1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>13 M Street</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>1012-MCity</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>012345612</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>065432112</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>www.msupplier1.com</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>contactm1@example.com</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>M013</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>M Supplier 2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>Contact M2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>13 M Avenue</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>2012-MVille</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>023456712</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>076543212</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>www.msupplier2.com</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>contactm2@example.com</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>0014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>N Supplier 1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Contact N1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14 N Street</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>1013-NCity</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>012345613</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>065432113</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>www.nsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>contactn1@example.com</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>N014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>N Supplier 2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Contact N2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>14 N Avenue</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>2013-NVille</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>023456713</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>076543213</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>www.nsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>contactn2@example.com</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>O Supplier 1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Contact O1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15 O Street</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>1014-OCity</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>012345614</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>065432114</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>www.osupplier1.com</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>contacto1@example.com</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2772,113 +2897,163 @@
           <t>30</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>4014</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>O015</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>O Supplier 2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Contact O2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>15 O Avenue</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ww</t>
+          <t>2014-OVille</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>023456714</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>076543214</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>www.osupplier2.com</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>contacto2@example.com</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>0016</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>P Supplier 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Contact P1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>16 P Street</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>1015-PCity</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+          <t>012345615</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>065432115</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>www.psupplier1.com</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>contactp1@example.com</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2886,223 +3061,1738 @@
           <t>30</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>P Supplier 2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Contact P2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>16 P Avenue</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2015-PVille</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>023456715</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>076543215</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>www.psupplier2.com</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>contactp2@example.com</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>0017</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+          <t>Q Supplier 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Contact Q1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>17 Q Street</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>1016-QCity</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>012345616</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>065432116</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>www.qsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>contactq1@example.com</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1010 - Intitulé du compte - 10</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ass</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ass</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>Q Supplier 2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Contact Q2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>17 Q Avenue</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2016-QVille</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ass</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>023456716</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>076543216</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>www.qsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>contactq2@example.com</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000 - Caisse - </t>
+          <t>2116</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1402 - Intitulé du compte - 14</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.0 (%)</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>4116</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>0018</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+          <t>R Supplier 1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Contact R1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>18 R Street</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1017-RCity</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>00988776</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>012345617</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>065432117</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>www.rsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>contactr1@example.com</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001 - Banque - </t>
+          <t>2017</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1011 - Intitulé du compte - 10</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8.1 (%)</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>R Supplier 2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Contact R2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>18 R Avenue</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2017-RVille</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>023456717</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>076543217</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>www.rsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>contactr2@example.com</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>4117</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0019</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S Supplier 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Contact S1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19 S Street</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1018-SCity</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>012345618</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>065432118</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>www.ssupplier1.com</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>contacts1@example.com</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S Supplier 2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Contact S2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19 S Avenue</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2018-SVille</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>023456718</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>076543218</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>www.ssupplier2.com</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>contacts2@example.com</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>3118</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>4118</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>T Supplier 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Contact T1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20 T Street</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1019-TCity</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>012345619</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>065432119</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>www.tsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>contactt1@example.com</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4019</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T020</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>T Supplier 2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Contact T2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20 T Avenue</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2019-TVille</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>023456719</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>076543219</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>www.tsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>contactt2@example.com</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3119</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0021</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>U Supplier 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Contact U1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>21 U Street</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1020-UCity</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>012345620</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>065432120</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>www.usupplier1.com</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>contactu1@example.com</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>U021</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>U Supplier 2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Contact U2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21 U Avenue</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2020-UVille</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>023456720</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>076543220</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>www.usupplier2.com</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>contactu2@example.com</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>V Supplier 1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Contact V1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22 V Street</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1021-VCity</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>012345621</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>065432121</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>www.vsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>contactv1@example.com</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4021</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>V022</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>V Supplier 2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Contact V2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22 V Avenue</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2021-VVille</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>023456721</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>076543221</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>www.vsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>contactv2@example.com</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2121</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3121</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0023</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>W Supplier 1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Contact W1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>23 W Street</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1022-WCity</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>012345622</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>065432122</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>www.wsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>contactw1@example.com</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3022</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>W023</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>W Supplier 2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Contact W2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>23 W Avenue</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2022-WVille</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>023456722</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>076543222</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>www.wsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>contactw2@example.com</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>X Supplier 1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Contact X1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>24 X Street</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1023-XCity</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>012345623</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>065432123</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>www.xsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>contactx1@example.com</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>X024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>X Supplier 2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Contact X2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>24 X Avenue</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2023-XVille</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>023456723</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>076543223</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>www.xsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>contactx2@example.com</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>3123</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Y Supplier 1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Contact Y1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>25 Y Street</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1024-YCity</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>012345624</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>065432124</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>www.ysupplier1.com</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>contacty1@example.com</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Y025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Y Supplier 2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Contact Y2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>25 Y Avenue</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2024-YVille</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>023456724</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>076543224</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>www.ysupplier2.com</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>contacty2@example.com</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Z Supplier 1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Contact Z1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>26 Z Street</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1025-ZCity</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>012345625</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>065432125</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>www.zsupplier1.com</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>contactz1@example.com</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>3025</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Z026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Z Supplier 2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Contact Z2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>26 Z Avenue</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-ZVille</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>023456725</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>076543225</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>www.zsupplier2.com</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>contactz2@example.com</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
